--- a/Data/EXCEL/Transfer/salemon/202206/6875-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/6875-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{43813A25-504D-4126-8952-7874A0051A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2DD27455-3430-4DF4-88F1-EB4CE57BBEB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="6875-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="18">
   <si>
     <t>月別</t>
   </si>
@@ -1207,13 +1207,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.25" customWidth="1"/>
-    <col min="2" max="5" width="11.125" customWidth="1"/>
-    <col min="6" max="16" width="10.625" customWidth="1"/>
-    <col min="17" max="17" width="11.625" customWidth="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="2" max="5" width="12.75" customWidth="1"/>
+    <col min="6" max="16" width="12.125" customWidth="1"/>
+    <col min="17" max="17" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1366,25 +1366,25 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>36.049999999999997</v>
+        <v>33.15</v>
       </c>
       <c r="C5" s="7">
-        <v>33.15</v>
+        <v>31.9</v>
       </c>
       <c r="D5" s="7">
-        <v>36.6</v>
+        <v>37.6</v>
       </c>
       <c r="E5" s="7">
-        <v>33</v>
+        <v>31.5</v>
       </c>
       <c r="F5" s="8">
-        <v>-2.9</v>
+        <v>-1.25</v>
       </c>
       <c r="G5" s="8">
-        <v>-8.0399999999999991</v>
+        <v>-3.77</v>
       </c>
       <c r="H5" s="9">
         <v>0</v>
@@ -1419,25 +1419,25 @@
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
-        <v>37.85</v>
+        <v>36.049999999999997</v>
       </c>
       <c r="C6" s="7">
-        <v>36.049999999999997</v>
+        <v>33.15</v>
       </c>
       <c r="D6" s="7">
-        <v>39.15</v>
+        <v>36.6</v>
       </c>
       <c r="E6" s="7">
-        <v>34.950000000000003</v>
+        <v>33</v>
       </c>
       <c r="F6" s="8">
-        <v>-1.8</v>
+        <v>-2.9</v>
       </c>
       <c r="G6" s="8">
-        <v>-4.76</v>
+        <v>-8.0399999999999991</v>
       </c>
       <c r="H6" s="9">
         <v>0</v>
@@ -1472,25 +1472,25 @@
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
-        <v>44.95</v>
+        <v>37.85</v>
       </c>
       <c r="C7" s="7">
-        <v>37.85</v>
+        <v>36.049999999999997</v>
       </c>
       <c r="D7" s="7">
-        <v>45.9</v>
+        <v>39.15</v>
       </c>
       <c r="E7" s="7">
-        <v>35.049999999999997</v>
+        <v>34.950000000000003</v>
       </c>
       <c r="F7" s="8">
-        <v>-7.1</v>
+        <v>-1.8</v>
       </c>
       <c r="G7" s="8">
-        <v>-15.8</v>
+        <v>-4.76</v>
       </c>
       <c r="H7" s="9">
         <v>0</v>
@@ -1525,25 +1525,25 @@
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7">
-        <v>49.65</v>
+        <v>44.95</v>
       </c>
       <c r="C8" s="7">
-        <v>44.95</v>
+        <v>37.85</v>
       </c>
       <c r="D8" s="7">
-        <v>59</v>
+        <v>45.9</v>
       </c>
       <c r="E8" s="7">
-        <v>43.3</v>
+        <v>35.049999999999997</v>
       </c>
       <c r="F8" s="8">
-        <v>-4.7</v>
+        <v>-7.1</v>
       </c>
       <c r="G8" s="8">
-        <v>-9.4700000000000006</v>
+        <v>-15.8</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
@@ -1578,25 +1578,25 @@
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>17</v>
+        <v>44593</v>
+      </c>
+      <c r="B9" s="7">
+        <v>49.65</v>
+      </c>
+      <c r="C9" s="7">
+        <v>44.95</v>
+      </c>
+      <c r="D9" s="7">
+        <v>59</v>
+      </c>
+      <c r="E9" s="7">
+        <v>43.3</v>
+      </c>
+      <c r="F9" s="8">
+        <v>-4.7</v>
+      </c>
+      <c r="G9" s="8">
+        <v>-9.4700000000000006</v>
       </c>
       <c r="H9" s="9">
         <v>0</v>
@@ -1631,7 +1631,7 @@
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>17</v>
@@ -1684,54 +1684,107 @@
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
+        <v>44531</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="9">
+        <v>0</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11" s="9">
+        <v>0</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M11" s="9">
+        <v>0</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
         <v>44501</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="9">
-        <v>0</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K11" s="9">
-        <v>0</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M11" s="9">
-        <v>0</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P11" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="9" t="s">
+      <c r="B12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="9">
+        <v>0</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12" s="9">
+        <v>0</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M12" s="9">
+        <v>0</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="9" t="s">
         <v>17</v>
       </c>
     </row>
